--- a/reports/二级子公司C_利润表_2026-07.xlsx
+++ b/reports/二级子公司C_利润表_2026-07.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>101689840</v>
+        <v>104504208</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>98748160</v>
+        <v>99277801</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>587165920</v>
+        <v>587294364</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>461440</v>
+        <v>458672</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2859280</v>
+        <v>2859773</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>403760</v>
+        <v>401565</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2501870</v>
+        <v>2501805</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>346080</v>
+        <v>344725</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2144460</v>
+        <v>2143988</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>323008</v>
+        <v>322456</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2001496</v>
+        <v>2000744</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>173040</v>
+        <v>173179</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1072230</v>
+        <v>1071732</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>138432</v>
+        <v>138871</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>857784</v>
+        <v>857379</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>99844080</v>
+        <v>102664740</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>96902400</v>
+        <v>97438333</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>92288000</v>
+        <v>92823991</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>547136000</v>
+        <v>547249224</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1384320</v>
+        <v>1390797</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>8577840</v>
+        <v>8579031</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>922880</v>
+        <v>925396</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5718560</v>
+        <v>5720359</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3460800</v>
+        <v>3461820</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>21444600</v>
+        <v>21453934</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>461440</v>
+        <v>460430</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2859280</v>
+        <v>2860651</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>346080</v>
+        <v>344596</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2144460</v>
+        <v>2145401</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>576800</v>
+        <v>573551</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>3574100</v>
+        <v>3575246</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>692160</v>
+        <v>688017</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4288920</v>
+        <v>4289549</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2884000</v>
+        <v>2868759</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>17870500</v>
+        <v>17869552</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>57680</v>
+        <v>51312</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>357410</v>
+        <v>360508</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1382408</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8574482</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>923928</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5715871</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>73726576</v>
+        <v>79071215</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>66170496</v>
+        <v>66564663</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>64786176</v>
+        <v>65172433</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>376505376</v>
+        <v>376449431</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1384320</v>
+        <v>1392230</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>8577840</v>
+        <v>8577543</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2317491</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>14298751</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>740092</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4576378</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>461420</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2860554</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>552344</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3432778</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>413420</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2574451</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>275275</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1716084</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>229347</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1429814</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1038240</v>
+        <v>1032928</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>6433380</v>
+        <v>6432868</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>807520</v>
+        <v>804790</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5003740</v>
+        <v>5002407</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>692160</v>
+        <v>691433</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4288920</v>
+        <v>4287178</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>5191200</v>
+        <v>5198803</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>32166900</v>
+        <v>32151634</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>230720</v>
+        <v>231579</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1429640</v>
+        <v>1428983</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>403760</v>
+        <v>362420</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2501870</v>
+        <v>2522575</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>461440</v>
+        <v>362420</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2859280</v>
+        <v>2522575</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>57680</v>
+        <v>51789</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>357410</v>
+        <v>360425</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>186184</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1297714</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>404612</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2502754</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>123553</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>865397</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>92440</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>649111</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>153769</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1081899</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>573438</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3575097</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>81914</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>576951</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>61495</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>432657</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>102681</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>720985</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>72048</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>504614</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51592</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>360394</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>41364</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>288297</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>31069</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>216222</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26117504</v>
+        <v>24962562</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31366384</v>
+        <v>28829369</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>231639</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1429947</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51592</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>360539</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>92288</v>
+        <v>82341</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>571856</v>
+        <v>576940</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26025216</v>
+        <v>25111860</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>3230080</v>
+        <v>2869776</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>20014960</v>
+        <v>20195445</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>22795136</v>
+        <v>22242084</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>22795136</v>
+        <v>22242084</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>22795136</v>
+        <v>22242084</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>22795136</v>
+        <v>22242084</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>22795136</v>
+        <v>22242084</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
